--- a/Data/Tables/EnemySkillDefine.xlsx
+++ b/Data/Tables/EnemySkillDefine.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowWidth="18052" windowHeight="8655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="120">
   <si>
     <t>技能名称（可以没有）</t>
   </si>
@@ -106,43 +106,76 @@
     <t>主动靠近玩家</t>
   </si>
   <si>
-    <t>毒蛇</t>
+    <t>主动靠近</t>
+  </si>
+  <si>
+    <t>毒蛇的冲刺技能</t>
   </si>
   <si>
     <t>主动靠近玩家，在玩家进入攻击范围后向玩家方向冲刺3m，冷却为3s。</t>
   </si>
   <si>
-    <t>群狼</t>
+    <t>进入一定范围</t>
+  </si>
+  <si>
+    <t>冲刺</t>
+  </si>
+  <si>
+    <t>群狼的群居技能</t>
   </si>
   <si>
     <t>主动靠近玩家，每有一只距离自身小于等于1的其他群狼，移动速度+0.1</t>
   </si>
   <si>
-    <t>穿山甲</t>
+    <t>范围内有其他单位</t>
+  </si>
+  <si>
+    <t>改变状态</t>
+  </si>
+  <si>
+    <t>穿山甲的获得护盾技能</t>
   </si>
   <si>
     <t>主动靠近玩家，首次受到伤害后速度降为0，缩成一团，获得等同于可以吸收自身最大生命值200%的护盾，持续5s，该状态下敌我弹幕均会被穿山甲阻挡。结束后失去护盾，移动速度恢复</t>
   </si>
   <si>
-    <t>毛绒怪堆</t>
+    <t>首次受伤</t>
+  </si>
+  <si>
+    <t>穿山甲的降低速度技能</t>
+  </si>
+  <si>
+    <t>毛绒怪堆的死亡生成技能</t>
   </si>
   <si>
     <t>主动靠近玩家，被消灭后在原地生成三只毛绒怪，毛绒怪生成时会在原地停留0.5s</t>
   </si>
   <si>
-    <t>瞿如</t>
+    <t>被消灭</t>
+  </si>
+  <si>
+    <t>生成</t>
+  </si>
+  <si>
+    <t>瞿如的发射声波技能</t>
   </si>
   <si>
     <t>主动靠近玩家，在玩家进入攻击范围后，向玩家发射声波，被击中后仅受到10点伤害，但移动速度降低0.5，持续3s,发射声波时不移动，冷却为5s。</t>
   </si>
   <si>
-    <t>穷奇</t>
+    <t>射击</t>
+  </si>
+  <si>
+    <t>穷奇的冲刺技能</t>
   </si>
   <si>
     <t>主动靠近玩家，在玩家进入攻击范围后向玩家方向冲刺直到地图边缘，在碰撞到边缘后以碰撞点为起点产生一个逐渐扩大的圆形震荡波（3m/s），玩家碰到震荡波等同于碰到穷奇，碰到边缘后穷奇眩晕5s，冷却15s。</t>
   </si>
   <si>
-    <t>孤魂</t>
+    <t>穷奇的震荡波技能</t>
+  </si>
+  <si>
+    <t>孤魂的无敌技能</t>
   </si>
   <si>
     <t>主动靠近玩家，在与玩家距离大于等于2时，不会受到伤害</t>
@@ -151,23 +184,32 @@
     <t>普通僵尸</t>
   </si>
   <si>
-    <t>小幽灵</t>
+    <t>小幽灵的射击技能</t>
   </si>
   <si>
     <t>尽可能与玩家保持3的距离，
 在玩家进入攻击范围后向玩家发射弹幕，冷却为3s。发射时移动速度降低，且自身模型晃动提示玩家。</t>
   </si>
   <si>
-    <t>鬼火幽灵</t>
+    <t>保持距离</t>
+  </si>
+  <si>
+    <t>鬼火幽灵的生成鬼火技能</t>
   </si>
   <si>
     <t>主动靠近玩家，玩家首次进入攻击范围后，生成一个以玩家为中心，半径为8的鬼火圈，鬼火圈在3s内缩小为半径为5的鬼火圈，玩家碰到后等同于碰到鬼火幽灵，持续3s。</t>
   </si>
   <si>
-    <t>吊死鬼</t>
-  </si>
-  <si>
-    <t>主动靠近玩家，在玩家进入攻击范围后将头抛向玩家，头向前移动至绳长（5）最远处慢慢拉回，身体与头通过绳子相连时受到伤害减少50%。玩家对绳子造成三次伤害后隔断绳子，身体倒下留下头。</t>
+    <t>首次进入</t>
+  </si>
+  <si>
+    <t>吊死鬼的攻击技能</t>
+  </si>
+  <si>
+    <t>主动靠近玩家，在玩家进入攻击范围后将头抛向玩家，头向前移动至绳长（5）最远处慢慢拉回，身体与头通过绳子相连时受到伤害减少50%。玩家对身体造成三次伤害后隔断绳子，身体倒下留下头。</t>
+  </si>
+  <si>
+    <t>吊死鬼的死亡技能</t>
   </si>
   <si>
     <t>吊死鬼的头</t>
@@ -176,109 +218,181 @@
     <t>主动靠近玩家，仅通过吊死鬼衍生，不会主动出现</t>
   </si>
   <si>
-    <t>魃</t>
+    <t>魃修为减少的技能</t>
   </si>
   <si>
     <t>主动靠近玩家，玩家的距离与魃小于等于3时修为减少0.3，且每当玩家在此距离内使用一次卡牌使自身的移速+0.1，伤害+5</t>
   </si>
   <si>
-    <t>烛阴</t>
-  </si>
-  <si>
-    <t>不移动，boss形象出现在地图上方，玩家视野缩小至半径为6的圆。进入关卡时和每隔20s在玩家视野外生成一个烛龙雕像，玩家只能攻击雕像来伤害烛龙。若烛龙雕像在玩家视野外，每隔2s会向玩家发射弹幕</t>
-  </si>
-  <si>
-    <t>浮尸</t>
+    <t>魃使用卡牌触发的技能1</t>
+  </si>
+  <si>
+    <t>玩家使用卡牌</t>
+  </si>
+  <si>
+    <t>魃使用卡牌触发的技能2</t>
+  </si>
+  <si>
+    <t>烛龙改变视野的技能</t>
+  </si>
+  <si>
+    <t>不移动，boss形象出现在地图上方，玩家视野缩小至半径为6的圆。进入关卡时和每隔20s在玩家视野外生成一个烛龙雕像，玩家只能攻击雕像来伤害烛龙。烛龙雕像每隔2s会向玩家发射弹幕</t>
+  </si>
+  <si>
+    <t>不移动</t>
+  </si>
+  <si>
+    <t>经历时间间隔</t>
+  </si>
+  <si>
+    <t>烛龙雕像的技能</t>
+  </si>
+  <si>
+    <t>浮尸的自爆技能</t>
   </si>
   <si>
     <t>主动靠近玩家，死亡0.5s后爆炸，影响范围为半径为0.5的圆</t>
   </si>
   <si>
-    <t>陆行鱼妖</t>
+    <t>陆行鱼妖的射击技能</t>
   </si>
   <si>
     <t>尽可能与玩家保持3的距离，
 在玩家进入攻击范围后瞄准3s之后向玩家投掷长矛，冷却为3s。瞄准时不移动。</t>
   </si>
   <si>
-    <t>提灯鬼</t>
+    <t>提灯鬼的射击技能</t>
   </si>
   <si>
     <t>不移动，每隔5s向玩家发射弹幕，每次发射完后瞬移到地图的随机地点（刷新点不会与玩家的距离小于等于1）</t>
   </si>
   <si>
-    <t>厚甲蟹</t>
-  </si>
-  <si>
-    <t>主动靠近玩家，生成时随机变化为一种颜色，红：受到的物理伤害-90%，蓝：受到的法术伤害-90%，绿：受到的卡牌伤害-90%</t>
-  </si>
-  <si>
-    <t>水型变幻怪</t>
+    <t>提灯鬼的移动技能</t>
+  </si>
+  <si>
+    <t>厚甲蟹的变色技能1</t>
+  </si>
+  <si>
+    <t>主动靠近玩家，生成时随机变化为一种颜色，红：受到的物理伤害-90%，蓝：受到的法术伤害-90%，绿：受到的武器伤害-90%</t>
+  </si>
+  <si>
+    <t>厚甲蟹的变色技能2</t>
+  </si>
+  <si>
+    <t>厚甲蟹的变色技能3</t>
+  </si>
+  <si>
+    <t>水型变幻怪的变形技能</t>
   </si>
   <si>
     <t>生成本怪时随机以另一个怪物的形象出现，受到一次伤害后消失5s，之后再次生成，生成五次后视为被消灭。</t>
   </si>
   <si>
-    <t>巨型蟾蜍</t>
-  </si>
-  <si>
-    <t>不移动，每隔2s向玩家方向跳跃位移2m，每次跳跃以落点为圆心生成半径为1的圆，此区域内所有单位的移动速度减1，区域持续4s，在玩家进入攻击范围后下次跳跃改为向玩家吐出舌头，碰到舌头等同于碰到举行蟾蜍。</t>
-  </si>
-  <si>
-    <t>化蛇</t>
+    <t>特殊</t>
+  </si>
+  <si>
+    <t>巨型蟾蜍的位移技能</t>
+  </si>
+  <si>
+    <t>不移动，每隔2s向玩家方向跳跃位移2m，每次跳跃以落点为圆心生成半径为1的圆，此区域内所有单位的移动速度减1，区域持续4s，在玩家进入攻击范围后下次跳跃改为向玩家吐出舌头，碰到舌头等同于碰到巨行蟾蜍。</t>
+  </si>
+  <si>
+    <t>巨型蟾蜍的攻击技能</t>
+  </si>
+  <si>
+    <t>化蛇的攻击技能</t>
   </si>
   <si>
     <t>主动靠近玩家，在玩家进入攻击范围后，向玩家发射大范围声波，击中后不受伤害仅减少1速度，持续5s。进入关卡产生向下的水流，使玩家获得该方向的1点移速。每当化蛇失去1/3的生命值，发出吼叫使所有单位移速降至1，顺时针90°改变一次水流方向</t>
   </si>
   <si>
-    <t>猎犬</t>
-  </si>
-  <si>
-    <t>主动靠近玩家，若玩家生命值不满，速度+0.3，攻击+10</t>
-  </si>
-  <si>
-    <t>猎户</t>
-  </si>
-  <si>
-    <t>在地图上无规则行走，碰到地图边缘改变移动方向，每隔10s停止移动1s在自己所在地防至一个陷阱。玩家踩到陷阱等同于碰到猎户并减少0.5速度3s</t>
-  </si>
-  <si>
-    <t>附灵钺</t>
+    <t>化蛇的改变水流技能</t>
+  </si>
+  <si>
+    <t>化蛇的水流影响技能1</t>
+  </si>
+  <si>
+    <t>化蛇的水流影响技能2</t>
+  </si>
+  <si>
+    <t>化蛇的水流影响技能3</t>
+  </si>
+  <si>
+    <t>化蛇的水流影响技能4</t>
+  </si>
+  <si>
+    <t>猎犬的检测生命值技能</t>
+  </si>
+  <si>
+    <t>主动靠近玩家，若玩家生命值不满，速度+0.3</t>
+  </si>
+  <si>
+    <t>猎户的放置陷阱技能</t>
+  </si>
+  <si>
+    <t>在地图上无规则行走，碰到地图边缘改变移动方向，每隔10s停止移动1s在自己所在地防至一个陷阱。玩家踩到陷阱等同于碰到猎户并减少0.5速度3s，陷阱被触发或持续15s后消失。</t>
+  </si>
+  <si>
+    <t>随机移动</t>
+  </si>
+  <si>
+    <t>陷阱的减速技能</t>
+  </si>
+  <si>
+    <t>附灵钺的合成技能</t>
   </si>
   <si>
     <t>主动靠近玩家，若和附灵戈相碰，结合成“礼器之灵”</t>
   </si>
   <si>
-    <t>附灵戈</t>
+    <t>附灵戈的合成技能</t>
   </si>
   <si>
     <t>主动靠近玩家，若和附灵钺相碰，结合成“礼器之灵”</t>
   </si>
   <si>
-    <t>礼器之灵</t>
+    <t>礼器之灵的攻击技能</t>
   </si>
   <si>
     <t>主动靠近玩家，仅通过附灵钺和附灵戈结合生成，不会主动生成。每隔1s发射八个方向的弹幕。</t>
   </si>
   <si>
-    <t>“钟馗”</t>
+    <t>“钟馗”的攻击技能</t>
   </si>
   <si>
     <t>尽可能与玩家保持5的距离，在玩家进入攻击范围后，在以玩家为圆心，半径为5的范围内画出预设的三种图样之一的图样作为攻击范围攻击玩家，作画结束后0.5s图样有伤害判定，持续1s后图样消失。玩家碰到图样等同于碰到“钟馗”</t>
   </si>
   <si>
-    <t>着魔的祭司</t>
+    <t>着魔的祭司的攻击技能</t>
   </si>
   <si>
     <t>尽可能与玩家保持6的距离，在玩家进入攻击范围后，蓄力1s向玩家发射弹幕，弹幕碰到边缘后会分分裂成四个方向的弹幕，分裂后的弹幕碰到边缘后会再分裂一次，此后的弹幕不再分裂，冷却4s。着魔的祭司在受到一次伤害后会立刻传送至地图的随机距离玩家大于等于2的地点，传送会打断蓄力动作。</t>
   </si>
   <si>
-    <t>刑天</t>
+    <t>着魔的祭司的传送技能</t>
+  </si>
+  <si>
+    <t>被攻击</t>
+  </si>
+  <si>
+    <t>刑天的扔斧头技能</t>
   </si>
   <si>
     <t>主动靠近玩家
 持有战斧时：在玩家进入攻击范围后，蓄力0.5s向玩家扔出战斧，战斧会停留在地图边缘。
 未持有战斧时：本体不会受到伤害，玩家需攻击战斧，速度+1，在玩家进入攻击范围后，蓄力0.5s冲向玩家直至地图边缘，重复三次。然后收回战斧并召唤一个附灵钺和一个附灵戈在自身的两侧</t>
+  </si>
+  <si>
+    <t>刑天的改变形态技能1</t>
+  </si>
+  <si>
+    <t>刑天的冲刺技能</t>
+  </si>
+  <si>
+    <t>刑天的收斧头技能</t>
+  </si>
+  <si>
+    <t>刑天的改变形态技能2</t>
   </si>
 </sst>
 </file>
@@ -1095,8 +1209,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表1" displayName="表1" ref="A3:K72" totalsRowShown="0">
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A3:K72" etc:filterBottomFollowUsedRange="0"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表1" displayName="表1" ref="A3:K88" totalsRowShown="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A3:K88" etc:filterBottomFollowUsedRange="0"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Key"/>
     <tableColumn id="2" name="ID"/>
@@ -1364,22 +1478,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K72"/>
-  <sheetFormatPr defaultColWidth="14.2916666666667" defaultRowHeight="14.25"/>
+  <dimension ref="A1:K88"/>
+  <sheetFormatPr defaultColWidth="14.2920353982301" defaultRowHeight="12.35"/>
   <cols>
-    <col min="1" max="1" width="8.25833333333333" style="3" customWidth="1"/>
-    <col min="2" max="2" width="7.29166666666667" style="3" customWidth="1"/>
-    <col min="3" max="3" width="38.75" style="3" customWidth="1"/>
-    <col min="4" max="4" width="38.5" style="1" customWidth="1"/>
-    <col min="5" max="5" width="14.2916666666667" style="1"/>
-    <col min="6" max="6" width="47.375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="27.625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="44.625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="28.125" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="14.2916666666667" style="1"/>
+    <col min="1" max="1" width="8.25663716814159" style="3" customWidth="1"/>
+    <col min="2" max="2" width="7.29203539823009" style="3" customWidth="1"/>
+    <col min="3" max="3" width="38.7522123893805" style="3" customWidth="1"/>
+    <col min="4" max="4" width="38.5044247787611" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14.2920353982301" style="1"/>
+    <col min="6" max="6" width="39.3008849557522" style="1" customWidth="1"/>
+    <col min="7" max="7" width="27.6283185840708" style="1" customWidth="1"/>
+    <col min="8" max="8" width="44.6283185840708" style="1" customWidth="1"/>
+    <col min="9" max="9" width="28.1238938053097" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="14.2920353982301" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="3:11">
+    <row r="1" s="1" customFormat="1" ht="12.4" spans="3:11">
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1408,7 +1522,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:11">
+    <row r="2" s="1" customFormat="1" ht="12.4" spans="1:11">
       <c r="A2" s="3"/>
       <c r="B2" s="3" t="s">
         <v>9</v>
@@ -1441,7 +1555,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:11">
+    <row r="3" s="1" customFormat="1" ht="12.4" spans="1:11">
       <c r="A3" s="4" t="s">
         <v>12</v>
       </c>
@@ -1476,7 +1590,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" s="2" customFormat="1" spans="1:5">
+    <row r="4" s="2" customFormat="1" ht="12.4" spans="1:5">
       <c r="A4" s="2">
         <v>1</v>
       </c>
@@ -1489,9 +1603,11 @@
       <c r="D4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E4" s="6"/>
-    </row>
-    <row r="5" s="2" customFormat="1" ht="28.5" spans="1:4">
+      <c r="E4" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" s="2" customFormat="1" ht="24.75" spans="1:11">
       <c r="A5" s="2">
         <v>2</v>
       </c>
@@ -1499,13 +1615,28 @@
         <v>2</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="6" s="2" customFormat="1" ht="28.5" spans="1:4">
+      <c r="G5" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" s="2">
+        <v>3</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K5" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" s="2" customFormat="1" ht="24.75" spans="1:11">
       <c r="A6" s="2">
         <v>3</v>
       </c>
@@ -1513,13 +1644,28 @@
         <v>3</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="7" s="2" customFormat="1" ht="57" spans="1:4">
+        <v>31</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H6" s="2">
+        <v>1</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K6" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" s="2" customFormat="1" ht="49.5" spans="1:11">
       <c r="A7" s="2">
         <v>4</v>
       </c>
@@ -1527,677 +1673,1270 @@
         <v>4</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K7" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" ht="12.4" spans="1:11">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K8" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="24.75" spans="1:11">
+      <c r="A9" s="2">
+        <v>5</v>
+      </c>
+      <c r="B9" s="2">
+        <v>5</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="K9" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" ht="37.15" spans="1:10">
+      <c r="A10" s="2">
+        <v>6</v>
+      </c>
+      <c r="B10" s="2">
+        <v>6</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H10" s="1">
+        <v>4</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" ht="61.9" spans="1:11">
+      <c r="A11" s="2">
+        <v>7</v>
+      </c>
+      <c r="B11" s="2">
+        <v>7</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H11" s="1">
+        <v>3</v>
+      </c>
+      <c r="J11" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="K11" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" ht="12.4" spans="1:10">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" ht="24.75" spans="1:11">
+      <c r="A13" s="2">
+        <v>8</v>
+      </c>
+      <c r="B13" s="2">
+        <v>8</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H13" s="1">
+        <v>2</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K13" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" ht="12.4" spans="1:5">
+      <c r="A14" s="2">
+        <v>9</v>
+      </c>
+      <c r="B14" s="2">
+        <v>9</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" ht="37.15" spans="1:10">
+      <c r="A15" s="2">
+        <v>10</v>
+      </c>
+      <c r="B15" s="2">
+        <v>10</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F15" s="1">
+        <v>3</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H15" s="1">
+        <v>3</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" ht="49.5" spans="1:10">
+      <c r="A16" s="2">
+        <v>11</v>
+      </c>
+      <c r="B16" s="2">
+        <v>11</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H16" s="1">
+        <v>5</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" ht="49.5" spans="1:5">
+      <c r="A17" s="1">
+        <v>12</v>
+      </c>
+      <c r="B17" s="3">
+        <v>12</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" ht="12.4" spans="1:11">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="K18" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" ht="12.4" spans="1:5">
+      <c r="A19" s="2">
+        <v>13</v>
+      </c>
+      <c r="B19" s="2">
+        <v>13</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" s="1" customFormat="1" ht="37.15" spans="1:11">
+      <c r="A20" s="2">
+        <v>14</v>
+      </c>
+      <c r="B20" s="2">
+        <v>14</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H20" s="1">
+        <v>3</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K20" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" s="1" customFormat="1" ht="12.4" spans="1:11">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="H21" s="1">
+        <v>3</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K21" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" s="1" customFormat="1" ht="12.4" spans="1:11">
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="H22" s="1">
+        <v>3</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K22" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" s="1" customFormat="1" ht="49.5" spans="1:11">
+      <c r="A23" s="2">
+        <v>15</v>
+      </c>
+      <c r="B23" s="2">
+        <v>15</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H23" s="1">
+        <v>20</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="K23" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" s="1" customFormat="1" ht="12.4" spans="1:10">
+      <c r="A24" s="2"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H24" s="1">
+        <v>2</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="25" s="1" customFormat="1" ht="24.75" spans="1:10">
+      <c r="A25" s="2">
+        <v>16</v>
+      </c>
+      <c r="B25" s="2">
+        <v>16</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="26" s="1" customFormat="1" ht="37.15" spans="1:10">
+      <c r="A26" s="2">
+        <v>17</v>
+      </c>
+      <c r="B26" s="2">
+        <v>17</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F26" s="1">
+        <v>3</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H26" s="1">
+        <v>3</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="27" s="1" customFormat="1" ht="37.15" spans="1:10">
+      <c r="A27" s="2">
+        <v>18</v>
+      </c>
+      <c r="B27" s="2">
+        <v>18</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H27" s="1">
+        <v>5</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="28" s="1" customFormat="1" ht="12.4" spans="1:8">
+      <c r="A28" s="2"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D28" s="2"/>
+      <c r="G28" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H28" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" s="1" customFormat="1" ht="37.15" spans="1:11">
+      <c r="A29" s="2">
+        <v>19</v>
+      </c>
+      <c r="B29" s="2">
+        <v>19</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H29" s="1">
+        <v>18</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K29" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" s="1" customFormat="1" ht="12.4" spans="1:11">
+      <c r="A30" s="2"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H30" s="1">
+        <v>18</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K30" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31" s="1" customFormat="1" ht="12.4" spans="1:11">
+      <c r="A31" s="2"/>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H31" s="1">
+        <v>18</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K31" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32" s="1" customFormat="1" ht="37.15" spans="1:5">
+      <c r="A32" s="2">
+        <v>20</v>
+      </c>
+      <c r="B32" s="2">
+        <v>20</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="33" s="1" customFormat="1" ht="61.9" spans="1:5">
+      <c r="A33" s="2">
+        <v>21</v>
+      </c>
+      <c r="B33" s="2">
+        <v>21</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="34" s="1" customFormat="1" ht="12.4" spans="1:10">
+      <c r="A34" s="2"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="35" s="1" customFormat="1" ht="61.9" spans="1:10">
+      <c r="A35" s="2">
+        <v>22</v>
+      </c>
+      <c r="B35" s="2">
+        <v>22</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H35" s="1">
+        <v>4</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="36" s="1" customFormat="1" ht="12.4" spans="1:3">
+      <c r="A36" s="2"/>
+      <c r="B36" s="2"/>
+      <c r="C36" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="37" s="1" customFormat="1" ht="12.4" spans="1:11">
+      <c r="A37" s="2"/>
+      <c r="B37" s="2"/>
+      <c r="C37" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H37" s="1">
+        <v>18</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K37" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="38" s="1" customFormat="1" ht="12.4" spans="1:11">
+      <c r="A38" s="2"/>
+      <c r="B38" s="2"/>
+      <c r="C38" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H38" s="1">
+        <v>18</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K38" s="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="39" s="1" customFormat="1" ht="12.4" spans="1:11">
+      <c r="A39" s="2"/>
+      <c r="B39" s="2"/>
+      <c r="C39" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H39" s="1">
+        <v>18</v>
+      </c>
+      <c r="J39" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K39" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="40" s="1" customFormat="1" ht="12.4" spans="1:11">
+      <c r="A40" s="2"/>
+      <c r="B40" s="2"/>
+      <c r="C40" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H40" s="1">
+        <v>18</v>
+      </c>
+      <c r="J40" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K40" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="41" s="1" customFormat="1" ht="12.4" spans="1:10">
+      <c r="A41" s="2">
+        <v>23</v>
+      </c>
+      <c r="B41" s="2">
+        <v>23</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J41" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="42" s="1" customFormat="1" ht="49.5" spans="1:11">
+      <c r="A42" s="2">
+        <v>24</v>
+      </c>
+      <c r="B42" s="2">
+        <v>24</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H42" s="1">
+        <v>10</v>
+      </c>
+      <c r="J42" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="K42" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" s="1" customFormat="1" ht="12.4" spans="1:10">
+      <c r="A43" s="2"/>
+      <c r="B43" s="2"/>
+      <c r="C43" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="J43" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="44" s="1" customFormat="1" ht="24.75" spans="1:11">
+      <c r="A44" s="2">
+        <v>25</v>
+      </c>
+      <c r="B44" s="2">
+        <v>25</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I44" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J44" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="K44" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" s="1" customFormat="1" ht="24.75" spans="1:11">
+      <c r="A45" s="2">
+        <v>26</v>
+      </c>
+      <c r="B45" s="2">
+        <v>26</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I45" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J45" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="K45" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" s="1" customFormat="1" ht="24.75" spans="1:10">
+      <c r="A46" s="2">
+        <v>27</v>
+      </c>
+      <c r="B46" s="2">
+        <v>27</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H46" s="1">
+        <v>1</v>
+      </c>
+      <c r="J46" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="47" s="1" customFormat="1" ht="61.9" spans="1:8">
+      <c r="A47" s="2">
+        <v>28</v>
+      </c>
+      <c r="B47" s="2">
+        <v>28</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F47" s="1">
+        <v>5</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H47" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" s="1" customFormat="1" ht="74.25" spans="1:10">
+      <c r="A48" s="2">
+        <v>29</v>
+      </c>
+      <c r="B48" s="2">
+        <v>29</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F48" s="1">
+        <v>6</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H48" s="1">
+        <v>6</v>
+      </c>
+      <c r="J48" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="49" s="1" customFormat="1" ht="12.4" spans="1:9">
+      <c r="A49" s="2"/>
+      <c r="B49" s="2"/>
+      <c r="C49" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="I49" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="50" s="1" customFormat="1" ht="86.65" spans="1:10">
+      <c r="A50" s="2">
         <v>30</v>
       </c>
-    </row>
-    <row r="8" s="1" customFormat="1" ht="28.5" spans="1:4">
-      <c r="A8" s="2">
-        <v>5</v>
-      </c>
-      <c r="B8" s="2">
-        <v>5</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D8" s="1" t="s">
+      <c r="B50" s="2">
+        <v>30</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H50" s="1">
+        <v>3</v>
+      </c>
+      <c r="J50" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="51" s="1" customFormat="1" ht="12.4" spans="1:10">
+      <c r="A51" s="2">
         <v>32</v>
       </c>
-    </row>
-    <row r="9" s="1" customFormat="1" ht="42.75" spans="1:4">
-      <c r="A9" s="2">
-        <v>6</v>
-      </c>
-      <c r="B9" s="2">
-        <v>6</v>
-      </c>
-      <c r="C9" s="2" t="s">
+      <c r="B51" s="2">
+        <v>32</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="J51" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D9" s="1" t="s">
+    </row>
+    <row r="52" s="1" customFormat="1" ht="12.4" spans="1:11">
+      <c r="A52" s="2">
+        <v>33</v>
+      </c>
+      <c r="B52" s="2">
+        <v>33</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H52" s="1">
+        <v>3</v>
+      </c>
+      <c r="J52" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K52" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="53" s="1" customFormat="1" ht="12.4" spans="1:10">
+      <c r="A53" s="2">
         <v>34</v>
       </c>
-    </row>
-    <row r="10" s="1" customFormat="1" ht="57" spans="1:4">
-      <c r="A10" s="2">
-        <v>7</v>
-      </c>
-      <c r="B10" s="2">
-        <v>7</v>
-      </c>
-      <c r="C10" s="2" t="s">
+      <c r="B53" s="2">
+        <v>34</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="J53" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="54" s="1" customFormat="1" ht="12.4" spans="1:10">
+      <c r="A54" s="2">
         <v>35</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="B54" s="2">
+        <v>35</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="J54" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="55" s="1" customFormat="1" spans="1:3">
+      <c r="A55" s="2">
         <v>36</v>
       </c>
-    </row>
-    <row r="11" s="1" customFormat="1" ht="28.5" spans="1:4">
-      <c r="A11" s="2">
-        <v>8</v>
-      </c>
-      <c r="B11" s="2">
-        <v>8</v>
-      </c>
-      <c r="C11" s="2" t="s">
+      <c r="B55" s="2">
+        <v>36</v>
+      </c>
+      <c r="C55" s="2"/>
+    </row>
+    <row r="56" s="1" customFormat="1" spans="1:3">
+      <c r="A56" s="2">
         <v>37</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="B56" s="2">
+        <v>37</v>
+      </c>
+      <c r="C56" s="2"/>
+    </row>
+    <row r="57" s="1" customFormat="1" spans="1:3">
+      <c r="A57" s="2">
         <v>38</v>
       </c>
-    </row>
-    <row r="12" s="1" customFormat="1" spans="1:4">
-      <c r="A12" s="2">
-        <v>9</v>
-      </c>
-      <c r="B12" s="2">
-        <v>9</v>
-      </c>
-      <c r="C12" s="2" t="s">
+      <c r="B57" s="2">
+        <v>38</v>
+      </c>
+      <c r="C57" s="2"/>
+    </row>
+    <row r="58" s="1" customFormat="1" spans="1:3">
+      <c r="A58" s="2">
         <v>39</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="13" s="1" customFormat="1" ht="42.75" spans="1:4">
-      <c r="A13" s="2">
-        <v>10</v>
-      </c>
-      <c r="B13" s="2">
-        <v>10</v>
-      </c>
-      <c r="C13" s="2" t="s">
+      <c r="B58" s="2">
+        <v>39</v>
+      </c>
+      <c r="C58" s="2"/>
+    </row>
+    <row r="59" s="1" customFormat="1" spans="1:3">
+      <c r="A59" s="2">
         <v>40</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="B59" s="2">
+        <v>40</v>
+      </c>
+      <c r="C59" s="2"/>
+    </row>
+    <row r="60" s="1" customFormat="1" spans="1:3">
+      <c r="A60" s="2">
         <v>41</v>
       </c>
-    </row>
-    <row r="14" s="1" customFormat="1" ht="57" spans="1:4">
-      <c r="A14" s="2">
-        <v>11</v>
-      </c>
-      <c r="B14" s="2">
-        <v>11</v>
-      </c>
-      <c r="C14" s="2" t="s">
+      <c r="B60" s="2">
+        <v>41</v>
+      </c>
+      <c r="C60" s="2"/>
+    </row>
+    <row r="61" s="1" customFormat="1" spans="1:3">
+      <c r="A61" s="2">
         <v>42</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="B61" s="2">
+        <v>42</v>
+      </c>
+      <c r="C61" s="2"/>
+    </row>
+    <row r="62" s="1" customFormat="1" ht="14.25" spans="1:4">
+      <c r="A62" s="2">
         <v>43</v>
       </c>
-    </row>
-    <row r="15" s="1" customFormat="1" ht="57" spans="1:4">
-      <c r="A15" s="1">
-        <v>12</v>
-      </c>
-      <c r="B15" s="3">
-        <v>12</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="16" s="1" customFormat="1" spans="1:4">
-      <c r="A16" s="2">
-        <v>13</v>
-      </c>
-      <c r="B16" s="2">
-        <v>13</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="17" s="1" customFormat="1" ht="42.75" spans="1:4">
-      <c r="A17" s="2">
-        <v>14</v>
-      </c>
-      <c r="B17" s="2">
-        <v>14</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="18" s="1" customFormat="1" ht="57" spans="1:4">
-      <c r="A18" s="2">
-        <v>15</v>
-      </c>
-      <c r="B18" s="2">
-        <v>15</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="19" s="1" customFormat="1" ht="28.5" spans="1:4">
-      <c r="A19" s="2">
-        <v>16</v>
-      </c>
-      <c r="B19" s="2">
-        <v>16</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="20" s="1" customFormat="1" ht="42.75" spans="1:4">
-      <c r="A20" s="2">
-        <v>17</v>
-      </c>
-      <c r="B20" s="2">
-        <v>17</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="21" s="1" customFormat="1" ht="28.5" spans="1:4">
-      <c r="A21" s="2">
-        <v>18</v>
-      </c>
-      <c r="B21" s="2">
-        <v>18</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="22" s="1" customFormat="1" ht="42.75" spans="1:4">
-      <c r="A22" s="2">
-        <v>19</v>
-      </c>
-      <c r="B22" s="2">
-        <v>19</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="23" s="1" customFormat="1" ht="28.5" spans="1:4">
-      <c r="A23" s="2">
-        <v>20</v>
-      </c>
-      <c r="B23" s="2">
-        <v>20</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="24" s="1" customFormat="1" ht="57" spans="1:4">
-      <c r="A24" s="2">
-        <v>21</v>
-      </c>
-      <c r="B24" s="2">
-        <v>21</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="25" s="1" customFormat="1" ht="71.25" spans="1:4">
-      <c r="A25" s="2">
-        <v>22</v>
-      </c>
-      <c r="B25" s="2">
-        <v>22</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="26" s="1" customFormat="1" spans="1:4">
-      <c r="A26" s="2">
-        <v>23</v>
-      </c>
-      <c r="B26" s="2">
-        <v>23</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="27" s="1" customFormat="1" ht="42.75" spans="1:4">
-      <c r="A27" s="2">
-        <v>24</v>
-      </c>
-      <c r="B27" s="2">
-        <v>24</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="28" s="1" customFormat="1" spans="1:4">
-      <c r="A28" s="2">
-        <v>25</v>
-      </c>
-      <c r="B28" s="2">
-        <v>25</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="29" s="1" customFormat="1" spans="1:4">
-      <c r="A29" s="2">
-        <v>26</v>
-      </c>
-      <c r="B29" s="2">
-        <v>26</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="30" s="1" customFormat="1" ht="28.5" spans="1:4">
-      <c r="A30" s="2">
-        <v>27</v>
-      </c>
-      <c r="B30" s="2">
-        <v>27</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="31" s="1" customFormat="1" ht="71.25" spans="1:4">
-      <c r="A31" s="2">
-        <v>28</v>
-      </c>
-      <c r="B31" s="2">
-        <v>28</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="32" s="1" customFormat="1" ht="85.5" spans="1:4">
-      <c r="A32" s="2">
-        <v>29</v>
-      </c>
-      <c r="B32" s="2">
-        <v>29</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="33" s="1" customFormat="1" ht="99.75" spans="1:4">
-      <c r="A33" s="2">
-        <v>30</v>
-      </c>
-      <c r="B33" s="2">
-        <v>30</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="34" s="1" customFormat="1" spans="1:3">
-      <c r="A34" s="2">
-        <v>31</v>
-      </c>
-      <c r="B34" s="2">
-        <v>31</v>
-      </c>
-      <c r="C34" s="3"/>
-    </row>
-    <row r="35" s="1" customFormat="1" spans="1:3">
-      <c r="A35" s="2">
-        <v>32</v>
-      </c>
-      <c r="B35" s="2">
-        <v>32</v>
-      </c>
-      <c r="C35" s="3"/>
-    </row>
-    <row r="36" s="1" customFormat="1" spans="1:3">
-      <c r="A36" s="2">
-        <v>33</v>
-      </c>
-      <c r="B36" s="2">
-        <v>33</v>
-      </c>
-      <c r="C36" s="2"/>
-    </row>
-    <row r="37" s="1" customFormat="1" spans="1:3">
-      <c r="A37" s="2">
-        <v>34</v>
-      </c>
-      <c r="B37" s="2">
-        <v>34</v>
-      </c>
-      <c r="C37" s="2"/>
-    </row>
-    <row r="38" s="1" customFormat="1" spans="1:3">
-      <c r="A38" s="2">
-        <v>35</v>
-      </c>
-      <c r="B38" s="2">
-        <v>35</v>
-      </c>
-      <c r="C38" s="2"/>
-    </row>
-    <row r="39" s="1" customFormat="1" spans="1:3">
-      <c r="A39" s="2">
-        <v>36</v>
-      </c>
-      <c r="B39" s="2">
-        <v>36</v>
-      </c>
-      <c r="C39" s="2"/>
-    </row>
-    <row r="40" s="1" customFormat="1" spans="1:3">
-      <c r="A40" s="2">
-        <v>37</v>
-      </c>
-      <c r="B40" s="2">
-        <v>37</v>
-      </c>
-      <c r="C40" s="2"/>
-    </row>
-    <row r="41" s="1" customFormat="1" spans="1:3">
-      <c r="A41" s="2">
-        <v>38</v>
-      </c>
-      <c r="B41" s="2">
-        <v>38</v>
-      </c>
-      <c r="C41" s="2"/>
-    </row>
-    <row r="42" s="1" customFormat="1" spans="1:3">
-      <c r="A42" s="2">
-        <v>39</v>
-      </c>
-      <c r="B42" s="2">
-        <v>39</v>
-      </c>
-      <c r="C42" s="2"/>
-    </row>
-    <row r="43" s="1" customFormat="1" spans="1:3">
-      <c r="A43" s="2">
-        <v>40</v>
-      </c>
-      <c r="B43" s="2">
-        <v>40</v>
-      </c>
-      <c r="C43" s="2"/>
-    </row>
-    <row r="44" s="1" customFormat="1" spans="1:3">
-      <c r="A44" s="2">
-        <v>41</v>
-      </c>
-      <c r="B44" s="2">
-        <v>41</v>
-      </c>
-      <c r="C44" s="2"/>
-    </row>
-    <row r="45" s="1" customFormat="1" spans="1:3">
-      <c r="A45" s="2">
-        <v>42</v>
-      </c>
-      <c r="B45" s="2">
-        <v>42</v>
-      </c>
-      <c r="C45" s="2"/>
-    </row>
-    <row r="46" s="1" customFormat="1" ht="15" spans="1:4">
-      <c r="A46" s="2">
+      <c r="B62" s="2">
         <v>43</v>
       </c>
-      <c r="B46" s="2">
-        <v>43</v>
-      </c>
-      <c r="C46" s="2"/>
-      <c r="D46" s="7"/>
-    </row>
-    <row r="47" s="1" customFormat="1" ht="15" spans="1:4">
-      <c r="A47" s="2">
-        <v>44</v>
-      </c>
-      <c r="B47" s="2">
-        <v>44</v>
-      </c>
-      <c r="C47" s="2"/>
-      <c r="D47" s="7"/>
-    </row>
-    <row r="48" s="1" customFormat="1" ht="15" spans="1:4">
-      <c r="A48" s="2">
-        <v>45</v>
-      </c>
-      <c r="B48" s="2">
-        <v>45</v>
-      </c>
-      <c r="C48" s="2"/>
-      <c r="D48" s="7"/>
-    </row>
-    <row r="49" s="1" customFormat="1" ht="15" spans="1:4">
-      <c r="A49" s="2">
-        <v>46</v>
-      </c>
-      <c r="B49" s="2">
-        <v>46</v>
-      </c>
-      <c r="C49" s="2"/>
-      <c r="D49" s="7"/>
-    </row>
-    <row r="50" s="1" customFormat="1" ht="15" spans="1:4">
-      <c r="A50" s="2">
-        <v>47</v>
-      </c>
-      <c r="B50" s="2">
-        <v>47</v>
-      </c>
-      <c r="C50" s="2"/>
-      <c r="D50" s="7"/>
-    </row>
-    <row r="51" s="1" customFormat="1" ht="15" spans="1:4">
-      <c r="A51" s="2">
-        <v>48</v>
-      </c>
-      <c r="B51" s="2">
-        <v>48</v>
-      </c>
-      <c r="C51" s="2"/>
-      <c r="D51" s="7"/>
-    </row>
-    <row r="52" s="1" customFormat="1" ht="15" spans="1:4">
-      <c r="A52" s="2">
-        <v>49</v>
-      </c>
-      <c r="B52" s="2">
-        <v>49</v>
-      </c>
-      <c r="C52" s="2"/>
-      <c r="D52" s="7"/>
-    </row>
-    <row r="53" s="1" customFormat="1" ht="15" spans="1:4">
-      <c r="A53" s="2">
-        <v>50</v>
-      </c>
-      <c r="B53" s="2">
-        <v>50</v>
-      </c>
-      <c r="C53" s="2"/>
-      <c r="D53" s="7"/>
-    </row>
-    <row r="54" s="1" customFormat="1" ht="15" spans="1:4">
-      <c r="A54" s="3"/>
-      <c r="B54" s="2"/>
-      <c r="C54" s="2"/>
-      <c r="D54" s="7"/>
-    </row>
-    <row r="55" s="1" customFormat="1" ht="15" spans="1:4">
-      <c r="A55" s="3"/>
-      <c r="B55" s="2"/>
-      <c r="C55" s="2"/>
-      <c r="D55" s="7"/>
-    </row>
-    <row r="56" s="1" customFormat="1" ht="15" spans="1:4">
-      <c r="A56" s="3"/>
-      <c r="B56" s="2"/>
-      <c r="C56" s="2"/>
-      <c r="D56" s="7"/>
-    </row>
-    <row r="57" s="1" customFormat="1" ht="15" spans="1:4">
-      <c r="A57" s="3"/>
-      <c r="B57" s="2"/>
-      <c r="C57" s="2"/>
-      <c r="D57" s="7"/>
-    </row>
-    <row r="58" s="1" customFormat="1" ht="15" spans="1:4">
-      <c r="A58" s="3"/>
-      <c r="B58" s="2"/>
-      <c r="C58" s="2"/>
-      <c r="D58" s="7"/>
-    </row>
-    <row r="59" s="1" customFormat="1" ht="15" spans="1:4">
-      <c r="A59" s="3"/>
-      <c r="B59" s="2"/>
-      <c r="C59" s="2"/>
-      <c r="D59" s="7"/>
-    </row>
-    <row r="60" s="1" customFormat="1" ht="15" spans="1:4">
-      <c r="A60" s="3"/>
-      <c r="B60" s="2"/>
-      <c r="C60" s="2"/>
-      <c r="D60" s="7"/>
-    </row>
-    <row r="61" s="1" customFormat="1" ht="15" spans="1:4">
-      <c r="A61" s="3"/>
-      <c r="B61" s="2"/>
-      <c r="C61" s="2"/>
-      <c r="D61" s="7"/>
-    </row>
-    <row r="62" s="1" customFormat="1" ht="15" spans="1:4">
-      <c r="A62" s="3"/>
-      <c r="B62" s="2"/>
       <c r="C62" s="2"/>
       <c r="D62" s="7"/>
     </row>
-    <row r="63" s="1" customFormat="1" ht="15" spans="1:4">
-      <c r="A63" s="3"/>
-      <c r="B63" s="2"/>
+    <row r="63" s="1" customFormat="1" ht="14.25" spans="1:4">
+      <c r="A63" s="2">
+        <v>44</v>
+      </c>
+      <c r="B63" s="2">
+        <v>44</v>
+      </c>
       <c r="C63" s="2"/>
       <c r="D63" s="7"/>
     </row>
-    <row r="64" s="1" customFormat="1" ht="15" spans="1:4">
-      <c r="A64" s="3"/>
-      <c r="B64" s="2"/>
+    <row r="64" s="1" customFormat="1" ht="14.25" spans="1:4">
+      <c r="A64" s="2">
+        <v>45</v>
+      </c>
+      <c r="B64" s="2">
+        <v>45</v>
+      </c>
       <c r="C64" s="2"/>
       <c r="D64" s="7"/>
     </row>
-    <row r="65" s="1" customFormat="1" ht="15" spans="1:4">
-      <c r="A65" s="3"/>
-      <c r="B65" s="2"/>
+    <row r="65" s="1" customFormat="1" ht="14.25" spans="1:4">
+      <c r="A65" s="2">
+        <v>46</v>
+      </c>
+      <c r="B65" s="2">
+        <v>46</v>
+      </c>
       <c r="C65" s="2"/>
       <c r="D65" s="7"/>
     </row>
-    <row r="66" s="1" customFormat="1" ht="15" spans="1:4">
-      <c r="A66" s="3"/>
-      <c r="B66" s="2"/>
+    <row r="66" s="1" customFormat="1" ht="14.25" spans="1:4">
+      <c r="A66" s="2">
+        <v>47</v>
+      </c>
+      <c r="B66" s="2">
+        <v>47</v>
+      </c>
       <c r="C66" s="2"/>
       <c r="D66" s="7"/>
     </row>
-    <row r="67" s="1" customFormat="1" ht="15" spans="1:4">
-      <c r="A67" s="3"/>
-      <c r="B67" s="2"/>
+    <row r="67" s="1" customFormat="1" ht="14.25" spans="1:4">
+      <c r="A67" s="2">
+        <v>48</v>
+      </c>
+      <c r="B67" s="2">
+        <v>48</v>
+      </c>
       <c r="C67" s="2"/>
       <c r="D67" s="7"/>
     </row>
-    <row r="68" s="1" customFormat="1" ht="15" spans="1:4">
-      <c r="A68" s="3"/>
-      <c r="B68" s="2"/>
+    <row r="68" s="1" customFormat="1" ht="14.25" spans="1:4">
+      <c r="A68" s="2">
+        <v>49</v>
+      </c>
+      <c r="B68" s="2">
+        <v>49</v>
+      </c>
       <c r="C68" s="2"/>
       <c r="D68" s="7"/>
     </row>
-    <row r="69" s="1" customFormat="1" ht="15" spans="1:4">
-      <c r="A69" s="3"/>
-      <c r="B69" s="2"/>
+    <row r="69" s="1" customFormat="1" ht="14.25" spans="1:4">
+      <c r="A69" s="2">
+        <v>50</v>
+      </c>
+      <c r="B69" s="2">
+        <v>50</v>
+      </c>
       <c r="C69" s="2"/>
       <c r="D69" s="7"/>
     </row>
-    <row r="70" s="1" customFormat="1" ht="15" spans="1:4">
+    <row r="70" s="1" customFormat="1" ht="14.25" spans="1:4">
       <c r="A70" s="3"/>
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
       <c r="D70" s="7"/>
     </row>
-    <row r="71" s="1" customFormat="1" ht="15" spans="1:4">
+    <row r="71" s="1" customFormat="1" ht="14.25" spans="1:4">
       <c r="A71" s="3"/>
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
       <c r="D71" s="7"/>
     </row>
-    <row r="72" s="1" customFormat="1" ht="15" spans="1:4">
+    <row r="72" s="1" customFormat="1" ht="14.25" spans="1:4">
       <c r="A72" s="3"/>
       <c r="B72" s="2"/>
       <c r="C72" s="2"/>
       <c r="D72" s="7"/>
+    </row>
+    <row r="73" s="1" customFormat="1" ht="14.25" spans="1:4">
+      <c r="A73" s="3"/>
+      <c r="B73" s="2"/>
+      <c r="C73" s="2"/>
+      <c r="D73" s="7"/>
+    </row>
+    <row r="74" s="1" customFormat="1" ht="14.25" spans="1:4">
+      <c r="A74" s="3"/>
+      <c r="B74" s="2"/>
+      <c r="C74" s="2"/>
+      <c r="D74" s="7"/>
+    </row>
+    <row r="75" s="1" customFormat="1" ht="14.25" spans="1:4">
+      <c r="A75" s="3"/>
+      <c r="B75" s="2"/>
+      <c r="C75" s="2"/>
+      <c r="D75" s="7"/>
+    </row>
+    <row r="76" s="1" customFormat="1" ht="14.25" spans="1:4">
+      <c r="A76" s="3"/>
+      <c r="B76" s="2"/>
+      <c r="C76" s="2"/>
+      <c r="D76" s="7"/>
+    </row>
+    <row r="77" s="1" customFormat="1" ht="14.25" spans="1:4">
+      <c r="A77" s="3"/>
+      <c r="B77" s="2"/>
+      <c r="C77" s="2"/>
+      <c r="D77" s="7"/>
+    </row>
+    <row r="78" s="1" customFormat="1" ht="14.25" spans="1:4">
+      <c r="A78" s="3"/>
+      <c r="B78" s="2"/>
+      <c r="C78" s="2"/>
+      <c r="D78" s="7"/>
+    </row>
+    <row r="79" s="1" customFormat="1" ht="14.25" spans="1:4">
+      <c r="A79" s="3"/>
+      <c r="B79" s="2"/>
+      <c r="C79" s="2"/>
+      <c r="D79" s="7"/>
+    </row>
+    <row r="80" s="1" customFormat="1" ht="14.25" spans="1:4">
+      <c r="A80" s="3"/>
+      <c r="B80" s="2"/>
+      <c r="C80" s="2"/>
+      <c r="D80" s="7"/>
+    </row>
+    <row r="81" s="1" customFormat="1" ht="14.25" spans="1:4">
+      <c r="A81" s="3"/>
+      <c r="B81" s="2"/>
+      <c r="C81" s="2"/>
+      <c r="D81" s="7"/>
+    </row>
+    <row r="82" s="1" customFormat="1" ht="14.25" spans="1:4">
+      <c r="A82" s="3"/>
+      <c r="B82" s="2"/>
+      <c r="C82" s="2"/>
+      <c r="D82" s="7"/>
+    </row>
+    <row r="83" s="1" customFormat="1" ht="14.25" spans="1:4">
+      <c r="A83" s="3"/>
+      <c r="B83" s="2"/>
+      <c r="C83" s="2"/>
+      <c r="D83" s="7"/>
+    </row>
+    <row r="84" s="1" customFormat="1" ht="14.25" spans="1:4">
+      <c r="A84" s="3"/>
+      <c r="B84" s="2"/>
+      <c r="C84" s="2"/>
+      <c r="D84" s="7"/>
+    </row>
+    <row r="85" s="1" customFormat="1" ht="14.25" spans="1:4">
+      <c r="A85" s="3"/>
+      <c r="B85" s="2"/>
+      <c r="C85" s="2"/>
+      <c r="D85" s="7"/>
+    </row>
+    <row r="86" s="1" customFormat="1" ht="14.25" spans="1:4">
+      <c r="A86" s="3"/>
+      <c r="B86" s="2"/>
+      <c r="C86" s="2"/>
+      <c r="D86" s="7"/>
+    </row>
+    <row r="87" s="1" customFormat="1" ht="14.25" spans="1:4">
+      <c r="A87" s="3"/>
+      <c r="B87" s="2"/>
+      <c r="C87" s="2"/>
+      <c r="D87" s="7"/>
+    </row>
+    <row r="88" s="1" customFormat="1" ht="14.25" spans="1:4">
+      <c r="A88" s="3"/>
+      <c r="B88" s="2"/>
+      <c r="C88" s="2"/>
+      <c r="D88" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
